--- a/couts.xlsx
+++ b/couts.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\FormationOpenClassRoom\Cours13 - Réalisez le cadrage d’un projet IA\FashionInsta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D77CC54-C7D0-499B-9EE0-7F43617ACFB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C673B3B-2EFE-4820-8D69-2DA7891E34FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9C354F4C-B153-4252-B584-9EFA1763D349}"/>
   </bookViews>
   <sheets>
-    <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
+    <sheet name="COUTS" sheetId="1" r:id="rId1"/>
+    <sheet name="RACI" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -24,8 +25,67 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>aceteam</author>
+  </authors>
+  <commentList>
+    <comment ref="E48" authorId="0" shapeId="0" xr:uid="{F1D274A8-2CF2-4CBD-A346-CA43E44CE47B}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>aceteam:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Indique la période de réalisation en nombre de semaines calendaire
+Si inférieur au nombre de semaines incompressible (voir plus haut) alors il faudra plus d'1 ressource à plein temps pour réaliser la phase</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G48" authorId="0" shapeId="0" xr:uid="{E85CDA95-103E-4BD4-BEB1-9C18CDEB96A2}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>aceteam:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Indique la charge réel en nombre de jours et semaines ouvrés</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="114">
   <si>
     <t>Ressources Humaines</t>
   </si>
@@ -84,12 +144,6 @@
     <t>Cout de maintenance</t>
   </si>
   <si>
-    <t>augmentera de 14% le CA Web sur 24 mois</t>
-  </si>
-  <si>
-    <t>augmentation du CA en magasin de 4 % sur 24 mois</t>
-  </si>
-  <si>
     <t>400k utilisateurs de l’application mobile / an</t>
   </si>
   <si>
@@ -126,12 +180,6 @@
     <t>CA moyen par magasin</t>
   </si>
   <si>
-    <t>%</t>
-  </si>
-  <si>
-    <t>€ / an</t>
-  </si>
-  <si>
     <t>CA physique (11 magasins)</t>
   </si>
   <si>
@@ -142,15 +190,6 @@
   </si>
   <si>
     <t>€</t>
-  </si>
-  <si>
-    <t>Gain Web</t>
-  </si>
-  <si>
-    <t>Gain magasin</t>
-  </si>
-  <si>
-    <t>CA magasin actuel</t>
   </si>
   <si>
     <t>Mois</t>
@@ -241,24 +280,181 @@
   </si>
   <si>
     <t>Staffing</t>
+  </si>
+  <si>
+    <t>Application Mobile et fonctionnalités</t>
+  </si>
+  <si>
+    <t>Exploitation</t>
+  </si>
+  <si>
+    <t>Monitoring</t>
+  </si>
+  <si>
+    <t>Réentraînement</t>
+  </si>
+  <si>
+    <t>Amélioration</t>
+  </si>
+  <si>
+    <t>Algorithme Similarité/Compatibilité</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>Responsable deréaliser la tache</t>
+  </si>
+  <si>
+    <t>Approuver la tache</t>
+  </si>
+  <si>
+    <t>Consultant conseil (souvant plusieurs sur une meme tache)</t>
+  </si>
+  <si>
+    <t>Informé après execution pour la suite des travaux</t>
+  </si>
+  <si>
+    <t>Tech Lead Software</t>
+  </si>
+  <si>
+    <t>Embedding catalogue Fashion Insta</t>
+  </si>
+  <si>
+    <t>Modèles IA et Datasets</t>
+  </si>
+  <si>
+    <t>Moteur de recommandation</t>
+  </si>
+  <si>
+    <t>Front End Developer</t>
+  </si>
+  <si>
+    <t>BackEnd Developer</t>
+  </si>
+  <si>
+    <t>Back-end developer</t>
+  </si>
+  <si>
+    <t>Front-end developer</t>
+  </si>
+  <si>
+    <t>Front-end dev</t>
+  </si>
+  <si>
+    <t>Back-end dev</t>
+  </si>
+  <si>
+    <t>Tech Lead Soft</t>
+  </si>
+  <si>
+    <t>Taux d'occupation journalié</t>
+  </si>
+  <si>
+    <t>sur la période donnée</t>
+  </si>
+  <si>
+    <t>Charge (JO)</t>
+  </si>
+  <si>
+    <t>Semaines (SC imposé)</t>
+  </si>
+  <si>
+    <t>pour 1 personne</t>
+  </si>
+  <si>
+    <t>Cadrage + sélection dataset</t>
+  </si>
+  <si>
+    <t>Préparation du jeu de test</t>
+  </si>
+  <si>
+    <t>Baseline + approche similaire</t>
+  </si>
+  <si>
+    <t>Approche compatibilité</t>
+  </si>
+  <si>
+    <t>Evaluation + comparaison</t>
+  </si>
+  <si>
+    <t>Synthèse + recommandation</t>
+  </si>
+  <si>
+    <t>Application et fonctionnalités</t>
+  </si>
+  <si>
+    <t>Embedding du catalogue Fashion Insta</t>
+  </si>
+  <si>
+    <t>Phase</t>
+  </si>
+  <si>
+    <t>JO</t>
+  </si>
+  <si>
+    <t>Tache</t>
+  </si>
+  <si>
+    <t>&lt;&lt; Nombre de semaines incompréssible pour réaliser la phase 1</t>
+  </si>
+  <si>
+    <t>&lt;&lt; Nombre de semaines incompréssible pour réaliser la phase 3</t>
+  </si>
+  <si>
+    <t>&lt;&lt; Nombre de semaines incompréssible pour réaliser la phase 2</t>
+  </si>
+  <si>
+    <t>&lt;&lt; Nombre de jours ouvrés incompressible pour réaliser la tâche</t>
+  </si>
+  <si>
+    <t>Gain Web estimé</t>
+  </si>
+  <si>
+    <t>Gain magasin espéré</t>
+  </si>
+  <si>
+    <t>Gain Web espéré</t>
+  </si>
+  <si>
+    <t>(24 mois)</t>
+  </si>
+  <si>
+    <t>Cout 24M</t>
+  </si>
+  <si>
+    <t>Cout Web estimé</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="9">
-    <numFmt numFmtId="168" formatCode="#,##0\ &quot;€&quot;\/\j\o\u\r"/>
-    <numFmt numFmtId="169" formatCode="#,##0\ &quot;€&quot;"/>
-    <numFmt numFmtId="170" formatCode="0.0%"/>
-    <numFmt numFmtId="172" formatCode="0\G\o"/>
-    <numFmt numFmtId="173" formatCode="0\h"/>
-    <numFmt numFmtId="176" formatCode="0.00\€\ \/\ \G\o"/>
-    <numFmt numFmtId="178" formatCode="0.00\€\ \/\ \h\ \G\P\U\ "/>
-    <numFmt numFmtId="180" formatCode="0.00&quot;€&quot;\ \/\ \v\C\P\U"/>
-    <numFmt numFmtId="181" formatCode="0.00&quot;€&quot;\ \/\ \h"/>
+  <numFmts count="13">
+    <numFmt numFmtId="164" formatCode="#,##0\ &quot;€&quot;\/\j\o\u\r"/>
+    <numFmt numFmtId="165" formatCode="#,##0\ &quot;€&quot;"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
+    <numFmt numFmtId="167" formatCode="0\G\o"/>
+    <numFmt numFmtId="168" formatCode="0\h"/>
+    <numFmt numFmtId="169" formatCode="0.00\€\ \/\ \G\o"/>
+    <numFmt numFmtId="170" formatCode="0.00\€\ \/\ \h\ \G\P\U\ "/>
+    <numFmt numFmtId="171" formatCode="0.00&quot;€&quot;\ \/\ \v\C\P\U"/>
+    <numFmt numFmtId="172" formatCode="0.00&quot;€&quot;\ \/\ \h"/>
+    <numFmt numFmtId="176" formatCode="0\%"/>
+    <numFmt numFmtId="178" formatCode="0\j"/>
+    <numFmt numFmtId="179" formatCode="0.0\s"/>
+    <numFmt numFmtId="181" formatCode="0.00\%"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -311,8 +507,74 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10.7"/>
+      <name val="Nunito"/>
+    </font>
+    <font>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="20"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="4"/>
+      <name val="Nunito"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="8" tint="-0.499984740745262"/>
+      <name val="Nunito"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -349,8 +611,50 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.34998626667073579"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -426,22 +730,235 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="160">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -453,226 +970,435 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="172" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="173" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="173" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="173" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="7" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="7" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -772,7 +1498,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Feuil1!$L$57</c:f>
+              <c:f>COUTS!$L$78</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -808,7 +1534,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Feuil1!$I$58:$I$64</c:f>
+              <c:f>COUTS!$I$79:$I$85</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
@@ -838,7 +1564,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Feuil1!$L$58:$L$64</c:f>
+              <c:f>COUTS!$L$79:$L$85</c:f>
               <c:numCache>
                 <c:formatCode>#\ ##0\ "€"</c:formatCode>
                 <c:ptCount val="7"/>
@@ -878,7 +1604,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Feuil1!$M$57</c:f>
+              <c:f>COUTS!$M$78</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -914,7 +1640,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Feuil1!$I$58:$I$64</c:f>
+              <c:f>COUTS!$I$79:$I$85</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
@@ -944,7 +1670,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Feuil1!$M$58:$M$64</c:f>
+              <c:f>COUTS!$M$79:$M$85</c:f>
               <c:numCache>
                 <c:formatCode>#\ ##0\ "€"</c:formatCode>
                 <c:ptCount val="7"/>
@@ -984,7 +1710,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Feuil1!$O$57</c:f>
+              <c:f>COUTS!$O$78</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1020,7 +1746,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Feuil1!$I$58:$I$64</c:f>
+              <c:f>COUTS!$I$79:$I$85</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
@@ -1050,30 +1776,30 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Feuil1!$O$58:$O$64</c:f>
+              <c:f>COUTS!$O$79:$O$85</c:f>
               <c:numCache>
                 <c:formatCode>#\ ##0\ "€"</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>-35202.17</c:v>
+                  <c:v>-19092.169999999998</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-26381.746547481689</c:v>
+                  <c:v>-9468.4132141483533</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>6159.2705610145276</c:v>
+                  <c:v>23875.937227681199</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>69417.317034132066</c:v>
+                  <c:v>87937.31703413208</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>169050.30465427856</c:v>
+                  <c:v>188373.63798761187</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>309942.55228990584</c:v>
+                  <c:v>330069.21895657253</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>496456.4189565726</c:v>
+                  <c:v>517386.41895657266</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1860,16 +2586,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>47624</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>166686</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>504825</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>80961</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>57149</xdr:colOff>
-      <xdr:row>66</xdr:row>
-      <xdr:rowOff>85724</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1571626</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2193,1310 +2919,2276 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DDBCC0B-5635-453A-A51A-B518A511B7EE}">
-  <dimension ref="A2:O82"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DDBCC0B-5635-453A-A51A-B518A511B7EE}">
+  <dimension ref="A2:P99"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="33.28515625" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.28515625" customWidth="1"/>
     <col min="4" max="4" width="21.85546875" customWidth="1"/>
     <col min="5" max="5" width="26.140625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="3" style="1" customWidth="1"/>
+    <col min="6" max="6" width="1.85546875" style="1" customWidth="1"/>
     <col min="7" max="12" width="11.42578125" style="1"/>
+    <col min="18" max="18" width="36.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="22" t="s">
+    <row r="2" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B3" s="147" t="s">
+        <v>101</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G3" s="144" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" s="144" t="s">
+        <v>1</v>
+      </c>
+      <c r="I3" s="144" t="s">
+        <v>3</v>
+      </c>
+      <c r="J3" s="144" t="s">
+        <v>2</v>
+      </c>
+      <c r="K3" s="144" t="s">
+        <v>85</v>
+      </c>
+      <c r="L3" s="144" t="s">
+        <v>86</v>
+      </c>
+      <c r="M3" s="145" t="s">
+        <v>87</v>
+      </c>
+      <c r="N3" s="150" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="4" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B4" s="148">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
+        <v>93</v>
+      </c>
+      <c r="G4" s="149"/>
+      <c r="H4" s="149">
+        <v>3</v>
+      </c>
+      <c r="I4" s="149">
+        <v>1</v>
+      </c>
+      <c r="J4" s="149">
+        <v>1</v>
+      </c>
+      <c r="K4" s="149"/>
+      <c r="L4" s="149"/>
+      <c r="M4" s="149"/>
+      <c r="N4" s="151">
+        <f>MAX(G4:M4)</f>
+        <v>3</v>
+      </c>
+      <c r="P4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="5" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B5" s="148">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G5" s="149"/>
+      <c r="H5" s="149">
+        <v>1</v>
+      </c>
+      <c r="I5" s="149"/>
+      <c r="J5" s="149"/>
+      <c r="K5" s="149"/>
+      <c r="L5" s="149"/>
+      <c r="M5" s="149"/>
+      <c r="N5" s="151">
+        <f t="shared" ref="N5:N20" si="0">MAX(G5:M5)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B6" s="148">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
+        <v>95</v>
+      </c>
+      <c r="G6" s="149">
+        <v>3</v>
+      </c>
+      <c r="H6" s="149"/>
+      <c r="I6" s="149"/>
+      <c r="J6" s="149"/>
+      <c r="K6" s="149"/>
+      <c r="L6" s="149"/>
+      <c r="M6" s="149"/>
+      <c r="N6" s="151">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B7" s="148">
+        <v>1</v>
+      </c>
+      <c r="D7" t="s">
+        <v>96</v>
+      </c>
+      <c r="G7" s="149">
+        <v>5</v>
+      </c>
+      <c r="H7" s="149"/>
+      <c r="I7" s="149"/>
+      <c r="J7" s="149"/>
+      <c r="K7" s="149"/>
+      <c r="L7" s="149"/>
+      <c r="M7" s="149"/>
+      <c r="N7" s="151">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B8" s="148">
+        <v>1</v>
+      </c>
+      <c r="D8" t="s">
+        <v>97</v>
+      </c>
+      <c r="G8" s="149"/>
+      <c r="H8" s="149"/>
+      <c r="I8" s="149"/>
+      <c r="J8" s="149"/>
+      <c r="K8" s="149"/>
+      <c r="L8" s="149"/>
+      <c r="M8" s="149"/>
+      <c r="N8" s="151">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B9" s="148">
+        <v>1</v>
+      </c>
+      <c r="D9" t="s">
+        <v>98</v>
+      </c>
+      <c r="G9" s="149"/>
+      <c r="H9" s="149"/>
+      <c r="I9" s="149"/>
+      <c r="J9" s="149"/>
+      <c r="K9" s="149"/>
+      <c r="L9" s="149"/>
+      <c r="M9" s="149"/>
+      <c r="N9" s="151">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B10" s="148"/>
+      <c r="G10" s="149"/>
+      <c r="H10" s="149"/>
+      <c r="I10" s="149"/>
+      <c r="J10" s="149"/>
+      <c r="K10" s="149"/>
+      <c r="L10" s="149"/>
+      <c r="M10" s="149"/>
+      <c r="N10" s="152">
+        <f>SUM(N4:N9)/5</f>
+        <v>2.4</v>
+      </c>
+      <c r="P10" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="11" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B11" s="148"/>
+      <c r="G11" s="149"/>
+      <c r="H11" s="149"/>
+      <c r="I11" s="149"/>
+      <c r="J11" s="149"/>
+      <c r="K11" s="149"/>
+      <c r="L11" s="149"/>
+      <c r="M11" s="149"/>
+      <c r="N11" s="149"/>
+    </row>
+    <row r="12" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B12" s="148">
+        <v>2</v>
+      </c>
+      <c r="D12" t="s">
+        <v>99</v>
+      </c>
+      <c r="G12" s="149"/>
+      <c r="H12" s="149"/>
+      <c r="I12" s="149">
+        <v>1</v>
+      </c>
+      <c r="J12" s="149">
+        <v>2</v>
+      </c>
+      <c r="K12" s="149">
+        <v>15</v>
+      </c>
+      <c r="L12" s="149">
+        <v>3</v>
+      </c>
+      <c r="M12" s="149">
+        <v>1</v>
+      </c>
+      <c r="N12" s="151">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B13" s="148">
+        <v>2</v>
+      </c>
+      <c r="D13" t="s">
+        <v>100</v>
+      </c>
+      <c r="G13" s="149"/>
+      <c r="H13" s="149">
+        <v>3</v>
+      </c>
+      <c r="I13" s="149">
+        <v>1</v>
+      </c>
+      <c r="J13" s="149">
+        <v>2</v>
+      </c>
+      <c r="K13" s="149"/>
+      <c r="L13" s="149"/>
+      <c r="M13" s="149"/>
+      <c r="N13" s="151">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B14" s="148">
+        <v>2</v>
+      </c>
+      <c r="D14" t="s">
+        <v>80</v>
+      </c>
+      <c r="G14" s="149">
+        <v>2</v>
+      </c>
+      <c r="H14" s="149">
+        <v>2</v>
+      </c>
+      <c r="I14" s="149">
+        <v>1</v>
+      </c>
+      <c r="J14" s="149">
+        <v>1</v>
+      </c>
+      <c r="K14" s="149"/>
+      <c r="L14" s="149">
+        <v>3</v>
+      </c>
+      <c r="M14" s="149">
+        <v>1</v>
+      </c>
+      <c r="N14" s="151">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B15" s="148"/>
+      <c r="G15" s="149"/>
+      <c r="H15" s="149"/>
+      <c r="I15" s="149"/>
+      <c r="J15" s="149"/>
+      <c r="K15" s="149"/>
+      <c r="L15" s="149"/>
+      <c r="M15" s="149"/>
+      <c r="N15" s="152">
+        <f>SUM(N12:N14)/5</f>
+        <v>4.2</v>
+      </c>
+      <c r="P15" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="16" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B16" s="148"/>
+      <c r="G16" s="149"/>
+      <c r="H16" s="149"/>
+      <c r="I16" s="149"/>
+      <c r="J16" s="149"/>
+      <c r="K16" s="149"/>
+      <c r="L16" s="149"/>
+      <c r="N16" s="149"/>
+    </row>
+    <row r="17" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B17" s="148">
+        <v>3</v>
+      </c>
+      <c r="D17" t="s">
+        <v>64</v>
+      </c>
+      <c r="G17" s="149"/>
+      <c r="H17" s="149"/>
+      <c r="I17" s="149">
+        <v>1</v>
+      </c>
+      <c r="J17" s="149">
+        <v>3</v>
+      </c>
+      <c r="K17" s="149"/>
+      <c r="L17" s="149"/>
+      <c r="M17" s="149"/>
+      <c r="N17" s="151">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B18" s="148">
+        <v>3</v>
+      </c>
+      <c r="D18" t="s">
+        <v>65</v>
+      </c>
+      <c r="G18" s="149"/>
+      <c r="H18" s="149"/>
+      <c r="I18" s="149">
+        <v>1</v>
+      </c>
+      <c r="J18" s="149">
+        <v>3</v>
+      </c>
+      <c r="K18" s="149"/>
+      <c r="L18" s="149"/>
+      <c r="M18" s="149"/>
+      <c r="N18" s="151">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B19" s="148">
+        <v>3</v>
+      </c>
+      <c r="D19" t="s">
+        <v>66</v>
+      </c>
+      <c r="G19" s="149">
+        <v>1</v>
+      </c>
+      <c r="H19" s="149">
+        <v>1</v>
+      </c>
+      <c r="I19" s="149">
+        <v>1</v>
+      </c>
+      <c r="J19" s="149">
+        <v>3</v>
+      </c>
+      <c r="K19" s="149"/>
+      <c r="L19" s="149"/>
+      <c r="M19" s="149"/>
+      <c r="N19" s="151">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B20" s="148">
+        <v>3</v>
+      </c>
+      <c r="D20" t="s">
+        <v>67</v>
+      </c>
+      <c r="G20" s="149">
+        <v>3</v>
+      </c>
+      <c r="H20" s="149">
+        <v>1</v>
+      </c>
+      <c r="I20" s="149">
+        <v>1</v>
+      </c>
+      <c r="J20" s="149"/>
+      <c r="K20" s="149"/>
+      <c r="L20" s="149"/>
+      <c r="M20" s="149"/>
+      <c r="N20" s="151">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="N21" s="152">
+        <f>SUM(N17:N20)/5</f>
+        <v>2.4</v>
+      </c>
+      <c r="P21" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="23" spans="2:16" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="23"/>
-      <c r="I2" s="30" t="s">
+      <c r="H23" s="56"/>
+      <c r="I23" s="57" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="31"/>
-      <c r="K2" s="38" t="s">
+      <c r="J23" s="58"/>
+      <c r="K23" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="39"/>
-    </row>
-    <row r="3" spans="2:14" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D3" s="7" t="s">
+      <c r="L23" s="60"/>
+    </row>
+    <row r="24" spans="2:16" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D24" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E24" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="8"/>
-      <c r="G3" s="24" t="s">
+      <c r="F24" s="5"/>
+      <c r="G24" s="49" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="25"/>
-      <c r="I3" s="32" t="s">
+      <c r="H24" s="50"/>
+      <c r="I24" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="J3" s="33"/>
-      <c r="K3" s="40" t="s">
+      <c r="J24" s="52"/>
+      <c r="K24" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="L3" s="41"/>
-    </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="G4" s="26"/>
-      <c r="H4" s="27"/>
-      <c r="I4" s="34"/>
-      <c r="J4" s="35"/>
-      <c r="K4" s="42"/>
-      <c r="L4" s="43"/>
-    </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="G5" s="28" t="s">
+      <c r="L24" s="54"/>
+    </row>
+    <row r="25" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="G25" s="18"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="22"/>
+      <c r="J25" s="23"/>
+      <c r="K25" s="26"/>
+      <c r="L25" s="27"/>
+    </row>
+    <row r="26" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="G26" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="H5" s="29" t="s">
+      <c r="H26" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="I5" s="36" t="s">
+      <c r="I26" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="J5" s="37" t="s">
+      <c r="J26" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="K5" s="44" t="s">
+      <c r="K26" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="L5" s="45" t="s">
+      <c r="L26" s="29" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="D6" s="11" t="s">
+    <row r="27" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="D27" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E27" s="8">
         <v>370</v>
       </c>
-      <c r="F6" s="20"/>
-      <c r="G6" s="13">
-        <v>12</v>
-      </c>
-      <c r="H6" s="14">
-        <f>G6*E6</f>
-        <v>4440</v>
-      </c>
-      <c r="I6" s="15">
-        <v>16</v>
-      </c>
-      <c r="J6" s="16">
-        <f>I6*E6</f>
-        <v>5920</v>
-      </c>
-      <c r="K6" s="17">
-        <v>7</v>
-      </c>
-      <c r="L6" s="18">
-        <f>K6*E6</f>
-        <v>2590</v>
-      </c>
-    </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="D7" s="11" t="s">
+      <c r="F27" s="16"/>
+      <c r="G27" s="9">
+        <f>SUM($H4:$H9)</f>
+        <v>4</v>
+      </c>
+      <c r="H27" s="10">
+        <f>G27*E27</f>
+        <v>1480</v>
+      </c>
+      <c r="I27" s="11">
+        <f>SUM($H12:$H14)</f>
+        <v>5</v>
+      </c>
+      <c r="J27" s="12">
+        <f>I27*E27</f>
+        <v>1850</v>
+      </c>
+      <c r="K27" s="13">
+        <f>SUM($H17:$H20)</f>
         <v>2</v>
       </c>
-      <c r="E7" s="12">
+      <c r="L27" s="14">
+        <f>K27*E27</f>
+        <v>740</v>
+      </c>
+    </row>
+    <row r="28" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="D28" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E28" s="8">
         <v>360</v>
       </c>
-      <c r="F7" s="20"/>
-      <c r="G7" s="13">
-        <v>7</v>
-      </c>
-      <c r="H7" s="14">
-        <f t="shared" ref="H7:H9" si="0">G7*E7</f>
-        <v>2520</v>
-      </c>
-      <c r="I7" s="15">
-        <v>14</v>
-      </c>
-      <c r="J7" s="16">
-        <f t="shared" ref="J7:J9" si="1">I7*E7</f>
-        <v>5040</v>
-      </c>
-      <c r="K7" s="17">
-        <v>10</v>
-      </c>
-      <c r="L7" s="18">
-        <f t="shared" ref="L7:L9" si="2">K7*E7</f>
-        <v>3600</v>
-      </c>
-    </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="D8" s="11" t="s">
+      <c r="F28" s="16"/>
+      <c r="G28" s="9">
+        <f>SUM($J4:$J9)</f>
+        <v>1</v>
+      </c>
+      <c r="H28" s="10">
+        <f t="shared" ref="H28:H33" si="1">G28*E28</f>
+        <v>360</v>
+      </c>
+      <c r="I28" s="11">
+        <f>SUM($J12:$J14)</f>
+        <v>5</v>
+      </c>
+      <c r="J28" s="12">
+        <f t="shared" ref="J28:J33" si="2">I28*E28</f>
+        <v>1800</v>
+      </c>
+      <c r="K28" s="13">
+        <f>SUM($J17:$J20)</f>
+        <v>9</v>
+      </c>
+      <c r="L28" s="14">
+        <f t="shared" ref="L28:L33" si="3">K28*E28</f>
+        <v>3240</v>
+      </c>
+    </row>
+    <row r="29" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="D29" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E8" s="12">
+      <c r="E29" s="8">
         <v>400</v>
       </c>
-      <c r="F8" s="20"/>
-      <c r="G8" s="13">
-        <v>5</v>
-      </c>
-      <c r="H8" s="14">
-        <f t="shared" si="0"/>
-        <v>2000</v>
-      </c>
-      <c r="I8" s="15">
-        <v>7</v>
-      </c>
-      <c r="J8" s="16">
+      <c r="F29" s="16"/>
+      <c r="G29" s="9">
+        <f>SUM($I4:$I9)</f>
+        <v>1</v>
+      </c>
+      <c r="H29" s="10">
+        <f t="shared" si="1"/>
+        <v>400</v>
+      </c>
+      <c r="I29" s="11">
+        <f>SUM($I12:$I14)</f>
+        <v>3</v>
+      </c>
+      <c r="J29" s="12">
+        <f t="shared" si="2"/>
+        <v>1200</v>
+      </c>
+      <c r="K29" s="13">
+        <f>SUM($I17:$I20)</f>
+        <v>4</v>
+      </c>
+      <c r="L29" s="14">
+        <f t="shared" si="3"/>
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="30" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="D30" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="E30" s="8">
+        <v>350</v>
+      </c>
+      <c r="F30" s="16"/>
+      <c r="G30" s="9">
+        <f>SUM($G4:$G9)</f>
+        <v>8</v>
+      </c>
+      <c r="H30" s="10">
         <f t="shared" si="1"/>
         <v>2800</v>
       </c>
-      <c r="K8" s="17">
+      <c r="I30" s="11">
+        <f>SUM($G12:$G14)</f>
+        <v>2</v>
+      </c>
+      <c r="J30" s="12">
+        <f t="shared" si="2"/>
+        <v>700</v>
+      </c>
+      <c r="K30" s="13">
+        <f>SUM($G17:$G20)</f>
+        <v>4</v>
+      </c>
+      <c r="L30" s="14">
+        <f t="shared" si="3"/>
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="31" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="D31" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="E31" s="8">
+        <v>350</v>
+      </c>
+      <c r="F31" s="16"/>
+      <c r="G31" s="9">
+        <f>SUM($K4:$K9)</f>
+        <v>0</v>
+      </c>
+      <c r="H31" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I31" s="11">
+        <f>SUM($K12:$K14)</f>
+        <v>15</v>
+      </c>
+      <c r="J31" s="12">
+        <f t="shared" si="2"/>
+        <v>5250</v>
+      </c>
+      <c r="K31" s="13">
+        <f>SUM($K17:$K20)</f>
+        <v>0</v>
+      </c>
+      <c r="L31" s="14">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="D32" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="E32" s="8">
+        <v>370</v>
+      </c>
+      <c r="F32" s="16"/>
+      <c r="G32" s="9">
+        <f>SUM($L4:$L9)</f>
+        <v>0</v>
+      </c>
+      <c r="H32" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I32" s="11">
+        <f>SUM($L12:$L14)</f>
+        <v>6</v>
+      </c>
+      <c r="J32" s="12">
+        <f t="shared" si="2"/>
+        <v>2220</v>
+      </c>
+      <c r="K32" s="13">
+        <f>SUM($L17:$L20)</f>
+        <v>0</v>
+      </c>
+      <c r="L32" s="14">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="D33" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="E33" s="8">
+        <v>400</v>
+      </c>
+      <c r="F33" s="16"/>
+      <c r="G33" s="9">
+        <f>SUM($M4:$M9)</f>
+        <v>0</v>
+      </c>
+      <c r="H33" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I33" s="11">
+        <f>SUM($M12:$M14)</f>
+        <v>2</v>
+      </c>
+      <c r="J33" s="12">
+        <f t="shared" si="2"/>
+        <v>800</v>
+      </c>
+      <c r="K33" s="13">
+        <f>SUM($M17:$M20)</f>
+        <v>0</v>
+      </c>
+      <c r="L33" s="14">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G34" s="18"/>
+      <c r="H34" s="19"/>
+      <c r="I34" s="22"/>
+      <c r="J34" s="23"/>
+      <c r="K34" s="26"/>
+      <c r="L34" s="27"/>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G35" s="18"/>
+      <c r="H35" s="19"/>
+      <c r="I35" s="22"/>
+      <c r="J35" s="23"/>
+      <c r="K35" s="26"/>
+      <c r="L35" s="27"/>
+    </row>
+    <row r="36" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E36" s="5"/>
+      <c r="F36" s="5"/>
+      <c r="G36" s="49" t="s">
+        <v>10</v>
+      </c>
+      <c r="H36" s="50"/>
+      <c r="I36" s="51" t="s">
+        <v>10</v>
+      </c>
+      <c r="J36" s="52"/>
+      <c r="K36" s="53" t="s">
+        <v>11</v>
+      </c>
+      <c r="L36" s="54"/>
+    </row>
+    <row r="37" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F37" s="5"/>
+      <c r="G37" s="49" t="s">
+        <v>7</v>
+      </c>
+      <c r="H37" s="50"/>
+      <c r="I37" s="51" t="s">
+        <v>8</v>
+      </c>
+      <c r="J37" s="52"/>
+      <c r="K37" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="L37" s="54"/>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G38" s="18"/>
+      <c r="H38" s="19"/>
+      <c r="I38" s="22"/>
+      <c r="J38" s="23"/>
+      <c r="K38" s="26"/>
+      <c r="L38" s="27"/>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G39" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H39" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="I39" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="J39" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="K39" s="28" t="s">
+        <v>14</v>
+      </c>
+      <c r="L39" s="29" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B40" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E40" s="43">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="F40" s="17"/>
+      <c r="G40" s="34">
+        <v>50</v>
+      </c>
+      <c r="H40" s="10">
+        <f>G40*E40</f>
+        <v>0.89999999999999991</v>
+      </c>
+      <c r="I40" s="35">
+        <v>150</v>
+      </c>
+      <c r="J40" s="12">
+        <f>I40*E40</f>
+        <v>2.6999999999999997</v>
+      </c>
+      <c r="K40" s="36">
+        <v>2000</v>
+      </c>
+      <c r="L40" s="14">
+        <f t="shared" ref="L40:L46" si="4">K40*E40*12</f>
+        <v>432</v>
+      </c>
+      <c r="N40" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B41" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E41" s="44">
+        <v>0.45</v>
+      </c>
+      <c r="F41" s="17"/>
+      <c r="G41" s="37">
+        <v>6</v>
+      </c>
+      <c r="H41" s="10">
+        <f t="shared" ref="H41:H46" si="5">G41*E41</f>
+        <v>2.7</v>
+      </c>
+      <c r="I41" s="39">
+        <v>18</v>
+      </c>
+      <c r="J41" s="12">
+        <f t="shared" ref="J41:J46" si="6">I41*E41</f>
+        <v>8.1</v>
+      </c>
+      <c r="K41" s="38">
+        <v>20</v>
+      </c>
+      <c r="L41" s="14">
+        <f t="shared" si="4"/>
+        <v>108</v>
+      </c>
+      <c r="N41" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B42" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E42" s="44">
+        <v>0.45</v>
+      </c>
+      <c r="F42" s="17"/>
+      <c r="G42" s="37">
+        <v>3</v>
+      </c>
+      <c r="H42" s="10">
+        <f t="shared" si="5"/>
+        <v>1.35</v>
+      </c>
+      <c r="I42" s="39">
+        <v>9</v>
+      </c>
+      <c r="J42" s="12">
+        <f t="shared" si="6"/>
+        <v>4.05</v>
+      </c>
+      <c r="K42" s="38">
+        <v>10</v>
+      </c>
+      <c r="L42" s="14">
+        <f t="shared" si="4"/>
+        <v>54</v>
+      </c>
+      <c r="N42" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B43" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E43" s="44">
+        <v>0.45</v>
+      </c>
+      <c r="F43" s="17"/>
+      <c r="G43" s="37">
+        <v>2</v>
+      </c>
+      <c r="H43" s="10">
+        <f t="shared" si="5"/>
+        <v>0.9</v>
+      </c>
+      <c r="I43" s="39">
+        <v>5</v>
+      </c>
+      <c r="J43" s="12">
+        <f t="shared" si="6"/>
+        <v>2.25</v>
+      </c>
+      <c r="K43" s="38">
+        <v>6</v>
+      </c>
+      <c r="L43" s="14">
+        <f t="shared" si="4"/>
+        <v>32.400000000000006</v>
+      </c>
+      <c r="N43" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B44" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E44" s="46">
+        <v>0.25</v>
+      </c>
+      <c r="F44" s="17"/>
+      <c r="G44" s="37">
+        <v>20</v>
+      </c>
+      <c r="H44" s="10">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="I44" s="39">
+        <v>730</v>
+      </c>
+      <c r="J44" s="12">
+        <f t="shared" si="6"/>
+        <v>182.5</v>
+      </c>
+      <c r="K44" s="38">
+        <v>730</v>
+      </c>
+      <c r="L44" s="14">
+        <f t="shared" si="4"/>
+        <v>2190</v>
+      </c>
+      <c r="N44" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B45" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E45" s="44">
+        <v>0.45</v>
+      </c>
+      <c r="F45" s="17"/>
+      <c r="G45" s="37">
+        <v>6</v>
+      </c>
+      <c r="H45" s="10">
+        <f t="shared" si="5"/>
+        <v>2.7</v>
+      </c>
+      <c r="I45" s="39">
+        <v>18</v>
+      </c>
+      <c r="J45" s="12">
+        <f t="shared" si="6"/>
+        <v>8.1</v>
+      </c>
+      <c r="K45" s="38">
+        <v>20</v>
+      </c>
+      <c r="L45" s="14">
+        <f t="shared" si="4"/>
+        <v>108</v>
+      </c>
+      <c r="N45" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B46" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E46" s="45">
+        <v>1.2E-5</v>
+      </c>
+      <c r="F46" s="17"/>
+      <c r="G46" s="40">
+        <v>10000</v>
+      </c>
+      <c r="H46" s="10">
+        <f t="shared" si="5"/>
+        <v>0.12000000000000001</v>
+      </c>
+      <c r="I46" s="41">
+        <v>900000</v>
+      </c>
+      <c r="J46" s="12">
+        <f t="shared" si="6"/>
+        <v>10.8</v>
+      </c>
+      <c r="K46" s="42">
+        <v>1000000</v>
+      </c>
+      <c r="L46" s="14">
+        <f t="shared" si="4"/>
+        <v>144</v>
+      </c>
+      <c r="N46" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="2"/>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A48" s="2"/>
+      <c r="D48" s="146" t="s">
+        <v>62</v>
+      </c>
+      <c r="E48" s="143" t="s">
+        <v>91</v>
+      </c>
+      <c r="F48" s="143"/>
+      <c r="G48" s="143" t="s">
+        <v>90</v>
+      </c>
+      <c r="H48" s="144" t="s">
         <v>1</v>
       </c>
-      <c r="L8" s="18">
-        <f t="shared" si="2"/>
-        <v>400</v>
-      </c>
-    </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="D9" s="11" t="s">
+      <c r="I48" s="144" t="s">
+        <v>2</v>
+      </c>
+      <c r="J48" s="144" t="s">
+        <v>3</v>
+      </c>
+      <c r="K48" s="144" t="s">
         <v>4</v>
       </c>
-      <c r="E9" s="12">
-        <v>350</v>
-      </c>
-      <c r="F9" s="20"/>
-      <c r="G9" s="13">
+      <c r="L48" s="144" t="s">
+        <v>85</v>
+      </c>
+      <c r="M48" s="144" t="s">
+        <v>86</v>
+      </c>
+      <c r="N48" s="145" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="49" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B49" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D49" s="78" t="s">
+        <v>7</v>
+      </c>
+      <c r="E49" s="79">
+        <v>3</v>
+      </c>
+      <c r="G49" s="1" t="str">
+        <f>SUM(G27:G33) &amp; "j"</f>
+        <v>14j</v>
+      </c>
+      <c r="H49" s="138">
+        <f>(G27/($E49*5))*100</f>
+        <v>26.666666666666668</v>
+      </c>
+      <c r="I49" s="138">
+        <f>(G28/($E49*5))*100</f>
+        <v>6.666666666666667</v>
+      </c>
+      <c r="J49" s="138">
+        <f>(G29/($E49*5))*100</f>
+        <v>6.666666666666667</v>
+      </c>
+      <c r="K49" s="138">
+        <f>(G30/($E49*5))*100</f>
+        <v>53.333333333333336</v>
+      </c>
+      <c r="L49" s="138">
+        <f>(G31/($E49*5))*100</f>
+        <v>0</v>
+      </c>
+      <c r="M49" s="138">
+        <f>(G32/($E49*5))*100</f>
+        <v>0</v>
+      </c>
+      <c r="N49" s="141">
+        <f>(G33/($E49*5))*100</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B50" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D50" s="78" t="s">
+        <v>8</v>
+      </c>
+      <c r="E50" s="79">
+        <v>5</v>
+      </c>
+      <c r="G50" s="1" t="str">
+        <f>SUM(I27:I33) &amp; "j"</f>
+        <v>38j</v>
+      </c>
+      <c r="H50" s="138">
+        <f>(I27/($E50*5))*100</f>
+        <v>20</v>
+      </c>
+      <c r="I50" s="138">
+        <f>(I28/($E50*5))*100</f>
+        <v>20</v>
+      </c>
+      <c r="J50" s="138">
+        <f>(I29/($E50*5))*100</f>
+        <v>12</v>
+      </c>
+      <c r="K50" s="138">
+        <f>(I30/($E50*5))*100</f>
+        <v>8</v>
+      </c>
+      <c r="L50" s="138">
+        <f>(I32/($E50*5))*100</f>
         <v>24</v>
       </c>
-      <c r="H9" s="14">
-        <f t="shared" si="0"/>
-        <v>8400</v>
-      </c>
-      <c r="I9" s="15">
-        <v>11</v>
-      </c>
-      <c r="J9" s="16">
-        <f t="shared" si="1"/>
-        <v>3850</v>
-      </c>
-      <c r="K9" s="17">
+      <c r="M50" s="138">
+        <f>(I32/($E50*5))*100</f>
+        <v>24</v>
+      </c>
+      <c r="N50" s="141">
+        <f>(I33/($E50*5))*100</f>
         <v>8</v>
       </c>
-      <c r="L9" s="18">
-        <f t="shared" si="2"/>
-        <v>2800</v>
-      </c>
-    </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="G10" s="26"/>
-      <c r="H10" s="27"/>
-      <c r="I10" s="34"/>
-      <c r="J10" s="35"/>
-      <c r="K10" s="42"/>
-      <c r="L10" s="43"/>
-    </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="G11" s="26"/>
-      <c r="H11" s="27"/>
-      <c r="I11" s="34"/>
-      <c r="J11" s="35"/>
-      <c r="K11" s="42"/>
-      <c r="L11" s="43"/>
-    </row>
-    <row r="12" spans="2:14" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="H12" s="25"/>
-      <c r="I12" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="J12" s="33"/>
-      <c r="K12" s="40" t="s">
-        <v>11</v>
-      </c>
-      <c r="L12" s="41"/>
-    </row>
-    <row r="13" spans="2:14" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="10" t="s">
+    </row>
+    <row r="51" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B51" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D51" s="81" t="s">
+        <v>9</v>
+      </c>
+      <c r="E51" s="83">
+        <v>3</v>
+      </c>
+      <c r="G51" s="83" t="str">
+        <f>SUM(K27:K33) &amp; "j"</f>
+        <v>19j</v>
+      </c>
+      <c r="H51" s="139">
+        <f>(K27/($E51*5))*100</f>
+        <v>13.333333333333334</v>
+      </c>
+      <c r="I51" s="139">
+        <f>(K28/($E51*5))*100</f>
+        <v>60</v>
+      </c>
+      <c r="J51" s="139">
+        <f>(K29/($E51*5))*100</f>
+        <v>26.666666666666668</v>
+      </c>
+      <c r="K51" s="139">
+        <f>(K30/($E51*5))*100</f>
+        <v>26.666666666666668</v>
+      </c>
+      <c r="L51" s="139">
+        <f>(K33/($E51*5))*100</f>
+        <v>0</v>
+      </c>
+      <c r="M51" s="139">
+        <f>(K32/($E51*5))*100</f>
+        <v>0</v>
+      </c>
+      <c r="N51" s="142">
+        <f>(K33/($E51*5))*100</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="D52" s="74"/>
+      <c r="E52" s="76"/>
+      <c r="F52" s="76"/>
+      <c r="G52" s="79"/>
+      <c r="H52" s="138"/>
+      <c r="I52" s="138"/>
+      <c r="J52" s="138"/>
+      <c r="K52" s="138"/>
+      <c r="L52" s="138"/>
+      <c r="M52" s="138"/>
+      <c r="N52" s="138"/>
+    </row>
+    <row r="53" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E53" s="82"/>
+      <c r="F53" s="83"/>
+    </row>
+    <row r="54" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="D54" s="75" t="s">
+        <v>17</v>
+      </c>
+      <c r="E54" s="76"/>
+      <c r="F54" s="76"/>
+      <c r="G54" s="84">
+        <f>SUM(H27:H33) + SUM(J27:J33) + SUM(H40:H46) + SUM(J40:J46)</f>
+        <v>19092.169999999998</v>
+      </c>
+      <c r="H54" s="85" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D55" s="81" t="s">
+        <v>18</v>
+      </c>
+      <c r="E55" s="83"/>
+      <c r="F55" s="83"/>
+      <c r="G55" s="86">
+        <f>SUM(L27:L33) + SUM(L40:L46)</f>
+        <v>10048.4</v>
+      </c>
+      <c r="H55" s="64" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="57" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="D57" s="87" t="s">
+        <v>40</v>
+      </c>
+      <c r="E57" s="77"/>
+      <c r="F57" s="77"/>
+      <c r="G57" s="77"/>
+      <c r="H57" s="88" t="s">
+        <v>6</v>
+      </c>
+      <c r="I57" s="89"/>
+      <c r="J57" s="5"/>
+    </row>
+    <row r="58" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="D58" s="78" t="s">
+        <v>19</v>
+      </c>
+      <c r="E58" s="79"/>
+      <c r="F58" s="79"/>
+      <c r="G58" s="79"/>
+      <c r="H58" s="92">
+        <v>400000</v>
+      </c>
+      <c r="I58" s="91" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="59" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="D59" s="78" t="s">
+        <v>20</v>
+      </c>
+      <c r="E59" s="79"/>
+      <c r="F59" s="79"/>
+      <c r="G59" s="79"/>
+      <c r="H59" s="92">
+        <v>40000</v>
+      </c>
+      <c r="I59" s="91" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="60" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="D60" s="78" t="s">
+        <v>29</v>
+      </c>
+      <c r="E60" s="79"/>
+      <c r="F60" s="79"/>
+      <c r="G60" s="79"/>
+      <c r="H60" s="92">
+        <v>5200000</v>
+      </c>
+      <c r="I60" s="91" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="61" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="D61" s="78" t="s">
         <v>30</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="E61" s="79"/>
+      <c r="F61" s="79"/>
+      <c r="G61" s="79"/>
+      <c r="H61" s="92">
+        <v>472000</v>
+      </c>
+      <c r="I61" s="91" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="62" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="D62" s="78" t="s">
+        <v>31</v>
+      </c>
+      <c r="E62" s="79"/>
+      <c r="F62" s="79"/>
+      <c r="G62" s="79"/>
+      <c r="H62" s="92">
+        <v>5200000</v>
+      </c>
+      <c r="I62" s="91" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="63" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D63" s="81" t="s">
+        <v>32</v>
+      </c>
+      <c r="E63" s="83"/>
+      <c r="F63" s="83"/>
+      <c r="G63" s="83"/>
+      <c r="H63" s="93">
+        <v>10400000</v>
+      </c>
+      <c r="I63" s="64" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="64" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K64" s="3"/>
+    </row>
+    <row r="65" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="D65" s="75" t="s">
+        <v>110</v>
+      </c>
+      <c r="E65" s="76" t="s">
+        <v>111</v>
+      </c>
+      <c r="F65" s="76"/>
+      <c r="G65" s="153">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="H65" s="134">
+        <f>H60*G65</f>
+        <v>728000.00000000012</v>
+      </c>
+      <c r="I65" s="85" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="66" spans="4:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D66" s="81" t="s">
+        <v>109</v>
+      </c>
+      <c r="E66" s="83" t="s">
+        <v>111</v>
+      </c>
+      <c r="F66" s="83"/>
+      <c r="G66" s="154">
+        <v>0.04</v>
+      </c>
+      <c r="H66" s="93">
+        <f>H62*G66</f>
+        <v>208000</v>
+      </c>
+      <c r="I66" s="64" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="67" spans="4:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D67" s="155" t="s">
+        <v>108</v>
+      </c>
+      <c r="E67" s="140" t="s">
+        <v>111</v>
+      </c>
+      <c r="F67" s="140"/>
+      <c r="G67" s="156">
+        <f>(H60+O85)/O85</f>
+        <v>11.050515068576756</v>
+      </c>
+      <c r="H67" s="157">
+        <f>H62*G67</f>
+        <v>57462678.35659913</v>
+      </c>
+      <c r="I67" s="63" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="68" spans="4:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D68" s="155" t="s">
+        <v>113</v>
+      </c>
+      <c r="E68" s="140" t="s">
+        <v>111</v>
+      </c>
+      <c r="F68" s="140"/>
+      <c r="G68" s="159">
+        <f>(N76/(H60*2))*100</f>
+        <v>0.37681701923076921</v>
+      </c>
+      <c r="H68" s="157">
+        <f>(G68*H60*2)/100</f>
+        <v>39188.97</v>
+      </c>
+      <c r="I68" s="63" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="70" spans="4:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="71" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="G71" s="94"/>
+      <c r="H71" s="76"/>
+      <c r="I71" s="76"/>
+      <c r="J71" s="95" t="s">
+        <v>43</v>
+      </c>
+      <c r="K71" s="96">
+        <f>K72/12</f>
+        <v>433333.33333333331</v>
+      </c>
+      <c r="L71" s="77"/>
+      <c r="M71" s="77" t="s">
+        <v>42</v>
+      </c>
+      <c r="N71" s="77" t="s">
+        <v>42</v>
+      </c>
+      <c r="O71" s="97"/>
+    </row>
+    <row r="72" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="G72" s="98"/>
+      <c r="H72" s="79"/>
+      <c r="I72" s="79"/>
+      <c r="J72" s="99" t="s">
+        <v>46</v>
+      </c>
+      <c r="K72" s="100">
+        <f>H60</f>
+        <v>5200000</v>
+      </c>
+      <c r="L72" s="101"/>
+      <c r="M72" s="101" t="s">
+        <v>41</v>
+      </c>
+      <c r="N72" s="101" t="s">
+        <v>49</v>
+      </c>
+      <c r="O72" s="80"/>
+    </row>
+    <row r="73" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="G73" s="98"/>
+      <c r="H73" s="79"/>
+      <c r="I73" s="79"/>
+      <c r="J73" s="99" t="s">
+        <v>44</v>
+      </c>
+      <c r="K73" s="102">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="L73" s="103"/>
+      <c r="M73" s="104">
+        <f>$G$55/12</f>
+        <v>837.36666666666667</v>
+      </c>
+      <c r="N73" s="104">
+        <f>G54</f>
+        <v>19092.169999999998</v>
+      </c>
+      <c r="O73" s="80"/>
+    </row>
+    <row r="74" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="G74" s="98"/>
+      <c r="H74" s="79"/>
+      <c r="I74" s="79"/>
+      <c r="J74" s="99" t="s">
+        <v>45</v>
+      </c>
+      <c r="K74" s="102">
+        <v>0.03</v>
+      </c>
+      <c r="L74" s="103"/>
+      <c r="M74" s="79">
+        <v>0</v>
+      </c>
+      <c r="N74" s="79">
+        <v>0</v>
+      </c>
+      <c r="O74" s="80"/>
+    </row>
+    <row r="75" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="G75" s="98"/>
+      <c r="H75" s="79"/>
+      <c r="I75" s="79"/>
+      <c r="J75" s="99" t="s">
+        <v>37</v>
+      </c>
+      <c r="K75" s="90">
+        <v>6</v>
+      </c>
+      <c r="L75" s="79"/>
+      <c r="M75" s="74"/>
+      <c r="N75" s="74"/>
+      <c r="O75" s="80"/>
+    </row>
+    <row r="76" spans="4:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G76" s="105"/>
+      <c r="H76" s="83"/>
+      <c r="I76" s="83"/>
+      <c r="J76" s="106" t="s">
+        <v>36</v>
+      </c>
+      <c r="K76" s="107">
+        <v>24</v>
+      </c>
+      <c r="L76" s="83"/>
+      <c r="M76" s="106" t="s">
+        <v>112</v>
+      </c>
+      <c r="N76" s="158">
+        <f>N73+M73*24</f>
+        <v>39188.97</v>
+      </c>
+      <c r="O76" s="62"/>
+    </row>
+    <row r="77" spans="4:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="78" spans="4:15" ht="39" x14ac:dyDescent="0.25">
+      <c r="G78" s="108" t="s">
+        <v>39</v>
+      </c>
+      <c r="H78" s="109" t="s">
+        <v>38</v>
+      </c>
+      <c r="I78" s="109" t="s">
+        <v>35</v>
+      </c>
+      <c r="J78" s="110" t="s">
+        <v>50</v>
+      </c>
+      <c r="K78" s="110" t="s">
+        <v>51</v>
+      </c>
+      <c r="L78" s="111" t="s">
+        <v>52</v>
+      </c>
+      <c r="M78" s="112" t="s">
+        <v>53</v>
+      </c>
+      <c r="N78" s="110" t="s">
+        <v>47</v>
+      </c>
+      <c r="O78" s="113" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="79" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="G79" s="114">
+        <v>0</v>
+      </c>
+      <c r="H79" s="30">
+        <v>0</v>
+      </c>
+      <c r="I79" s="15">
+        <v>0</v>
+      </c>
+      <c r="J79" s="31">
+        <v>0</v>
+      </c>
+      <c r="K79" s="31">
+        <f t="shared" ref="K79:K85" si="7">$K$73*(I79/24)^1.5</f>
+        <v>0</v>
+      </c>
+      <c r="L79" s="48">
+        <v>0</v>
+      </c>
+      <c r="M79" s="47">
+        <v>0</v>
+      </c>
+      <c r="N79" s="32">
+        <f>$N$73</f>
+        <v>19092.169999999998</v>
+      </c>
+      <c r="O79" s="115">
+        <f t="shared" ref="O79:O85" si="8">(M79-L79)-N79</f>
+        <v>-19092.169999999998</v>
+      </c>
+    </row>
+    <row r="80" spans="4:15" x14ac:dyDescent="0.25">
+      <c r="G80" s="114">
+        <f t="shared" ref="G80:G85" si="9">ROW(H80)-ROW($H$78)-1</f>
+        <v>1</v>
+      </c>
+      <c r="H80" s="30">
+        <f t="shared" ref="H80:H85" si="10">(100/$K$75)*G80</f>
+        <v>16.666666666666668</v>
+      </c>
+      <c r="I80" s="15">
+        <f t="shared" ref="I80:I85" si="11">($K$76/$K$75)*G80</f>
+        <v>4</v>
+      </c>
+      <c r="J80" s="31">
+        <f>$K$74*(I80/24)^1.5</f>
+        <v>2.0412414523193144E-3</v>
+      </c>
+      <c r="K80" s="31">
+        <f t="shared" si="7"/>
+        <v>9.5257934441568028E-3</v>
+      </c>
+      <c r="L80" s="48">
+        <f>((I80-I79)*(J80*$K$71))+L79</f>
+        <v>3538.1518506868115</v>
+      </c>
+      <c r="M80" s="47">
+        <f t="shared" ref="M80:M85" si="12">((I80-I79)*(K80*$K$71))+M79</f>
+        <v>16511.375303205125</v>
+      </c>
+      <c r="N80" s="32">
+        <f t="shared" ref="N80:N85" si="13">($M$73*(I80-I79))+N79</f>
+        <v>22441.636666666665</v>
+      </c>
+      <c r="O80" s="115">
+        <f t="shared" si="8"/>
+        <v>-9468.4132141483533</v>
+      </c>
+    </row>
+    <row r="81" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="G81" s="114">
+        <f t="shared" si="9"/>
+        <v>2</v>
+      </c>
+      <c r="H81" s="30">
+        <f t="shared" si="10"/>
+        <v>33.333333333333336</v>
+      </c>
+      <c r="I81" s="15">
+        <f t="shared" si="11"/>
+        <v>8</v>
+      </c>
+      <c r="J81" s="31">
+        <f t="shared" ref="J81:J85" si="14">$K$74*(I81/24)^1.5</f>
+        <v>5.773502691896258E-3</v>
+      </c>
+      <c r="K81" s="31">
+        <f t="shared" si="7"/>
+        <v>2.6943012562182539E-2</v>
+      </c>
+      <c r="L81" s="48">
+        <f t="shared" ref="L81:L85" si="15">((I81-I80)*(J81*$K$71))+L80</f>
+        <v>13545.556516640325</v>
+      </c>
+      <c r="M81" s="47">
+        <f t="shared" si="12"/>
+        <v>63212.597077654857</v>
+      </c>
+      <c r="N81" s="32">
+        <f>($M$73*(I81-I80))+N80</f>
+        <v>25791.103333333333</v>
+      </c>
+      <c r="O81" s="115">
+        <f t="shared" si="8"/>
+        <v>23875.937227681199</v>
+      </c>
+    </row>
+    <row r="82" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="G82" s="114">
+        <f t="shared" si="9"/>
+        <v>3</v>
+      </c>
+      <c r="H82" s="30">
+        <f t="shared" si="10"/>
+        <v>50</v>
+      </c>
+      <c r="I82" s="15">
+        <f t="shared" si="11"/>
         <v>12</v>
       </c>
-      <c r="E13" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F13" s="8"/>
-      <c r="G13" s="24" t="s">
-        <v>7</v>
-      </c>
-      <c r="H13" s="25"/>
-      <c r="I13" s="32" t="s">
-        <v>8</v>
-      </c>
-      <c r="J13" s="33"/>
-      <c r="K13" s="40" t="s">
-        <v>9</v>
-      </c>
-      <c r="L13" s="41"/>
-    </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="G14" s="26"/>
-      <c r="H14" s="27"/>
-      <c r="I14" s="34"/>
-      <c r="J14" s="35"/>
-      <c r="K14" s="42"/>
-      <c r="L14" s="43"/>
-    </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="G15" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="H15" s="29" t="s">
-        <v>15</v>
-      </c>
-      <c r="I15" s="36" t="s">
-        <v>14</v>
-      </c>
-      <c r="J15" s="37" t="s">
-        <v>15</v>
-      </c>
-      <c r="K15" s="44" t="s">
-        <v>14</v>
-      </c>
-      <c r="L15" s="45" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B16" s="6" t="s">
+      <c r="J82" s="31">
+        <f t="shared" si="14"/>
+        <v>1.0606601717798213E-2</v>
+      </c>
+      <c r="K82" s="31">
+        <f t="shared" si="7"/>
+        <v>4.9497474683058332E-2</v>
+      </c>
+      <c r="L82" s="48">
+        <f t="shared" si="15"/>
+        <v>31930.332827490562</v>
+      </c>
+      <c r="M82" s="47">
+        <f t="shared" si="12"/>
+        <v>149008.21986162264</v>
+      </c>
+      <c r="N82" s="32">
+        <f t="shared" si="13"/>
+        <v>29140.57</v>
+      </c>
+      <c r="O82" s="115">
+        <f t="shared" si="8"/>
+        <v>87937.31703413208</v>
+      </c>
+    </row>
+    <row r="83" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="G83" s="114">
+        <f t="shared" si="9"/>
+        <v>4</v>
+      </c>
+      <c r="H83" s="30">
+        <f t="shared" si="10"/>
+        <v>66.666666666666671</v>
+      </c>
+      <c r="I83" s="15">
+        <f t="shared" si="11"/>
+        <v>16</v>
+      </c>
+      <c r="J83" s="31">
+        <f t="shared" si="14"/>
+        <v>1.6329931618554516E-2</v>
+      </c>
+      <c r="K83" s="31">
+        <f t="shared" si="7"/>
+        <v>7.6206347553254422E-2</v>
+      </c>
+      <c r="L83" s="48">
+        <f t="shared" si="15"/>
+        <v>60235.54763298505</v>
+      </c>
+      <c r="M83" s="47">
+        <f t="shared" si="12"/>
+        <v>281099.2222872636</v>
+      </c>
+      <c r="N83" s="32">
+        <f t="shared" si="13"/>
+        <v>32490.036666666667</v>
+      </c>
+      <c r="O83" s="115">
+        <f t="shared" si="8"/>
+        <v>188373.63798761187</v>
+      </c>
+    </row>
+    <row r="84" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="G84" s="114">
+        <f t="shared" si="9"/>
+        <v>5</v>
+      </c>
+      <c r="H84" s="30">
+        <f t="shared" si="10"/>
+        <v>83.333333333333343</v>
+      </c>
+      <c r="I84" s="15">
+        <f t="shared" si="11"/>
+        <v>20</v>
+      </c>
+      <c r="J84" s="31">
+        <f t="shared" si="14"/>
+        <v>2.282177322938192E-2</v>
+      </c>
+      <c r="K84" s="31">
+        <f t="shared" si="7"/>
+        <v>0.10650160840378231</v>
+      </c>
+      <c r="L84" s="48">
+        <f t="shared" si="15"/>
+        <v>99793.287897247035</v>
+      </c>
+      <c r="M84" s="47">
+        <f t="shared" si="12"/>
+        <v>465702.01018715295</v>
+      </c>
+      <c r="N84" s="32">
+        <f t="shared" si="13"/>
+        <v>35839.503333333334</v>
+      </c>
+      <c r="O84" s="115">
+        <f t="shared" si="8"/>
+        <v>330069.21895657253</v>
+      </c>
+    </row>
+    <row r="85" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G85" s="116">
+        <f t="shared" si="9"/>
+        <v>6</v>
+      </c>
+      <c r="H85" s="117">
+        <f t="shared" si="10"/>
+        <v>100</v>
+      </c>
+      <c r="I85" s="118">
+        <f t="shared" si="11"/>
         <v>24</v>
       </c>
-      <c r="D16" s="11" t="s">
+      <c r="J85" s="119">
+        <f t="shared" si="14"/>
+        <v>0.03</v>
+      </c>
+      <c r="K85" s="119">
+        <f t="shared" si="7"/>
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="L85" s="120">
+        <f t="shared" si="15"/>
+        <v>151793.28789724704</v>
+      </c>
+      <c r="M85" s="121">
+        <f t="shared" si="12"/>
+        <v>708368.67685381963</v>
+      </c>
+      <c r="N85" s="122">
+        <f t="shared" si="13"/>
+        <v>39188.97</v>
+      </c>
+      <c r="O85" s="123">
+        <f t="shared" si="8"/>
+        <v>517386.41895657266</v>
+      </c>
+    </row>
+    <row r="88" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="89" spans="2:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B89" s="124" t="s">
+        <v>54</v>
+      </c>
+      <c r="C89" s="125"/>
+      <c r="D89" s="126" t="s">
+        <v>22</v>
+      </c>
+      <c r="E89" s="76"/>
+      <c r="F89" s="76"/>
+      <c r="G89" s="76"/>
+      <c r="H89" s="125" t="s">
+        <v>21</v>
+      </c>
+      <c r="I89" s="85"/>
+    </row>
+    <row r="90" spans="2:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B90" s="127" t="s">
+        <v>55</v>
+      </c>
+      <c r="C90" s="74"/>
+      <c r="D90" s="128" t="s">
+        <v>26</v>
+      </c>
+      <c r="E90" s="129"/>
+      <c r="F90" s="79"/>
+      <c r="G90" s="79"/>
+      <c r="H90" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="I90" s="91"/>
+    </row>
+    <row r="91" spans="2:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B91" s="78" t="s">
+        <v>56</v>
+      </c>
+      <c r="C91" s="74"/>
+      <c r="D91" s="130" t="s">
+        <v>26</v>
+      </c>
+      <c r="E91" s="79"/>
+      <c r="F91" s="79"/>
+      <c r="G91" s="79"/>
+      <c r="H91" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="I91" s="91"/>
+    </row>
+    <row r="92" spans="2:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B92" s="127" t="s">
+        <v>57</v>
+      </c>
+      <c r="C92" s="74"/>
+      <c r="D92" s="128" t="s">
+        <v>26</v>
+      </c>
+      <c r="E92" s="129"/>
+      <c r="F92" s="79"/>
+      <c r="G92" s="79"/>
+      <c r="H92" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="I92" s="91"/>
+    </row>
+    <row r="93" spans="2:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B93" s="131" t="s">
+        <v>58</v>
+      </c>
+      <c r="C93" s="74"/>
+      <c r="D93" s="128" t="s">
+        <v>24</v>
+      </c>
+      <c r="E93" s="79"/>
+      <c r="F93" s="79"/>
+      <c r="G93" s="79"/>
+      <c r="H93" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="E16" s="75">
-        <v>1.7999999999999999E-2</v>
-      </c>
-      <c r="F16" s="21"/>
-      <c r="G16" s="66">
-        <v>50</v>
-      </c>
-      <c r="H16" s="14">
-        <f>G16*E16</f>
-        <v>0.89999999999999991</v>
-      </c>
-      <c r="I16" s="67">
-        <v>150</v>
-      </c>
-      <c r="J16" s="16">
-        <f>I16*E16</f>
-        <v>2.6999999999999997</v>
-      </c>
-      <c r="K16" s="68">
-        <v>2000</v>
-      </c>
-      <c r="L16" s="18">
-        <f>K16*E16*12</f>
-        <v>432</v>
-      </c>
-      <c r="N16" t="s">
+      <c r="I93" s="91"/>
+    </row>
+    <row r="94" spans="2:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B94" s="127" t="s">
+        <v>59</v>
+      </c>
+      <c r="C94" s="74"/>
+      <c r="D94" s="128" t="s">
+        <v>26</v>
+      </c>
+      <c r="E94" s="79"/>
+      <c r="F94" s="79"/>
+      <c r="G94" s="79"/>
+      <c r="H94" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="I94" s="91"/>
+    </row>
+    <row r="95" spans="2:15" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B95" s="132" t="s">
+        <v>60</v>
+      </c>
+      <c r="C95" s="82"/>
+      <c r="D95" s="133" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B17" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D17" s="11" t="s">
+      <c r="E95" s="83"/>
+      <c r="F95" s="83"/>
+      <c r="G95" s="83"/>
+      <c r="H95" s="82" t="s">
         <v>27</v>
       </c>
-      <c r="E17" s="76">
-        <v>0.45</v>
-      </c>
-      <c r="F17" s="21"/>
-      <c r="G17" s="69">
-        <v>6</v>
-      </c>
-      <c r="H17" s="14">
-        <f t="shared" ref="H17:H22" si="3">G17*E17</f>
-        <v>2.7</v>
-      </c>
-      <c r="I17" s="71">
-        <v>18</v>
-      </c>
-      <c r="J17" s="16">
-        <f t="shared" ref="J17:J22" si="4">I17*E17</f>
-        <v>8.1</v>
-      </c>
-      <c r="K17" s="70">
-        <v>20</v>
-      </c>
-      <c r="L17" s="18">
-        <f>K17*E17*12</f>
-        <v>108</v>
-      </c>
-      <c r="N17" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B18" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D18" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="E18" s="76">
-        <v>0.45</v>
-      </c>
-      <c r="F18" s="21"/>
-      <c r="G18" s="69">
-        <v>3</v>
-      </c>
-      <c r="H18" s="14">
-        <f t="shared" si="3"/>
-        <v>1.35</v>
-      </c>
-      <c r="I18" s="71">
-        <v>9</v>
-      </c>
-      <c r="J18" s="16">
-        <f t="shared" si="4"/>
-        <v>4.05</v>
-      </c>
-      <c r="K18" s="70">
-        <v>10</v>
-      </c>
-      <c r="L18" s="18">
-        <f>K18*E18*12</f>
-        <v>54</v>
-      </c>
-      <c r="N18" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B19" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D19" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="E19" s="76">
-        <v>0.45</v>
-      </c>
-      <c r="F19" s="21"/>
-      <c r="G19" s="69">
-        <v>2</v>
-      </c>
-      <c r="H19" s="14">
-        <f t="shared" si="3"/>
-        <v>0.9</v>
-      </c>
-      <c r="I19" s="71">
-        <v>5</v>
-      </c>
-      <c r="J19" s="16">
-        <f t="shared" si="4"/>
-        <v>2.25</v>
-      </c>
-      <c r="K19" s="70">
-        <v>6</v>
-      </c>
-      <c r="L19" s="18">
-        <f>K19*E19*12</f>
-        <v>32.400000000000006</v>
-      </c>
-      <c r="N19" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B20" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D20" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="E20" s="78">
-        <v>0.25</v>
-      </c>
-      <c r="F20" s="21"/>
-      <c r="G20" s="69">
-        <v>20</v>
-      </c>
-      <c r="H20" s="14">
-        <f t="shared" si="3"/>
-        <v>5</v>
-      </c>
-      <c r="I20" s="71">
-        <v>730</v>
-      </c>
-      <c r="J20" s="16">
-        <f t="shared" si="4"/>
-        <v>182.5</v>
-      </c>
-      <c r="K20" s="70">
-        <v>730</v>
-      </c>
-      <c r="L20" s="18">
-        <f>K20*E20*12</f>
-        <v>2190</v>
-      </c>
-      <c r="N20" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B21" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D21" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="E21" s="76">
-        <v>0.45</v>
-      </c>
-      <c r="F21" s="21"/>
-      <c r="G21" s="69">
-        <v>6</v>
-      </c>
-      <c r="H21" s="14">
-        <f t="shared" si="3"/>
-        <v>2.7</v>
-      </c>
-      <c r="I21" s="71">
-        <v>18</v>
-      </c>
-      <c r="J21" s="16">
-        <f t="shared" si="4"/>
-        <v>8.1</v>
-      </c>
-      <c r="K21" s="70">
-        <v>20</v>
-      </c>
-      <c r="L21" s="18">
-        <f>K21*E21*12</f>
-        <v>108</v>
-      </c>
-      <c r="N21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B22" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="D22" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="E22" s="77">
-        <v>1.2E-5</v>
-      </c>
-      <c r="F22" s="21"/>
-      <c r="G22" s="72">
-        <v>10000</v>
-      </c>
-      <c r="H22" s="14">
-        <f t="shared" si="3"/>
-        <v>0.12000000000000001</v>
-      </c>
-      <c r="I22" s="73">
-        <v>900000</v>
-      </c>
-      <c r="J22" s="16">
-        <f t="shared" si="4"/>
-        <v>10.8</v>
-      </c>
-      <c r="K22" s="74">
-        <v>1000000</v>
-      </c>
-      <c r="L22" s="18">
-        <f>K22*E22*12</f>
-        <v>144</v>
-      </c>
-      <c r="N22" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="5"/>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A24" s="5"/>
-      <c r="G24" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="H24" s="85" t="s">
-        <v>1</v>
-      </c>
-      <c r="I24" s="85" t="s">
-        <v>2</v>
-      </c>
-      <c r="J24" s="85" t="s">
-        <v>3</v>
-      </c>
-      <c r="K24" s="85" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="D25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E25" t="str">
-        <f xml:space="preserve">  ROUNDUP(SUM(G6:G9)/7,0) &amp; " Semaines - Charge " &amp; SUM(G6:G9) &amp; " Jours"</f>
-        <v>7 Semaines - Charge 48 Jours</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H25" s="48">
-        <f>(G6/SUM(G6:G9))*100</f>
-        <v>25</v>
-      </c>
-      <c r="I25" s="48">
-        <f>(G7/SUM(G6:G9))*100</f>
-        <v>14.583333333333334</v>
-      </c>
-      <c r="J25" s="48">
-        <f>(G8/SUM(G6:G9))*100</f>
-        <v>10.416666666666668</v>
-      </c>
-      <c r="K25" s="48">
-        <f>(G9/SUM(G6:G9))*100</f>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="D26" t="s">
-        <v>8</v>
-      </c>
-      <c r="E26" t="str">
-        <f xml:space="preserve">  ROUNDUP(SUM(I6:I9)/7,0) &amp; " Semaines - Charge " &amp; SUM(I6:I9) &amp; " Jours"</f>
-        <v>7 Semaines - Charge 48 Jours</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H26" s="48">
-        <f>(I6/SUM(I6:I9))*100</f>
-        <v>33.333333333333329</v>
-      </c>
-      <c r="I26" s="48">
-        <f>(I7/SUM(I6:I9))*100</f>
-        <v>29.166666666666668</v>
-      </c>
-      <c r="J26" s="48">
-        <f>(I8/SUM(I6:I9))*100</f>
-        <v>14.583333333333334</v>
-      </c>
-      <c r="K26" s="48">
-        <f>(I9/SUM(I6:I9))*100</f>
-        <v>22.916666666666664</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="D27" t="s">
-        <v>9</v>
-      </c>
-      <c r="E27" t="str">
-        <f xml:space="preserve">  ROUNDUP(SUM(K6:K9)/7,0) &amp; " Semaines - Charge " &amp; SUM(K6:K9) &amp; " Jours"</f>
-        <v>4 Semaines - Charge 26 Jours</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H27" s="48">
-        <f>(K6/SUM(K6:K9))*100</f>
-        <v>26.923076923076923</v>
-      </c>
-      <c r="I27" s="48">
-        <f>(K7/SUM(K6:K9))*100</f>
-        <v>38.461538461538467</v>
-      </c>
-      <c r="J27" s="48">
-        <f>(K8/SUM(K6:K9))*100</f>
-        <v>3.8461538461538463</v>
-      </c>
-      <c r="K27" s="48">
-        <f>(K9/SUM(K6:K9))*100</f>
-        <v>30.76923076923077</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="E28"/>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="D29" t="s">
-        <v>17</v>
-      </c>
-      <c r="G29" s="2">
-        <f>SUM(H6:H9) + SUM(J6:J9) + SUM(H16:H22) + SUM(J16:J22)</f>
-        <v>35202.17</v>
-      </c>
-      <c r="H29" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="D30" t="s">
-        <v>18</v>
-      </c>
-      <c r="G30" s="2">
-        <f>SUM(L6:L9) + SUM(L16:L22)</f>
-        <v>12458.4</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="D32" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="E32" s="8"/>
-      <c r="F32" s="8"/>
-      <c r="G32" s="8"/>
-      <c r="H32" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="I32" s="9"/>
-      <c r="J32" s="8"/>
-    </row>
-    <row r="33" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D33" t="s">
-        <v>19</v>
-      </c>
-      <c r="H33" s="46">
-        <v>7</v>
-      </c>
-      <c r="I33" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="34" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D34" t="s">
-        <v>20</v>
-      </c>
-      <c r="H34" s="46">
-        <v>2</v>
-      </c>
-      <c r="I34" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="35" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D35" t="s">
-        <v>21</v>
-      </c>
-      <c r="H35" s="47">
-        <v>400000</v>
-      </c>
-      <c r="I35" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="36" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D36" t="s">
-        <v>22</v>
-      </c>
-      <c r="H36" s="47">
-        <v>40000</v>
-      </c>
-      <c r="I36" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="37" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D37" t="s">
-        <v>31</v>
-      </c>
-      <c r="H37" s="47">
-        <v>5200000</v>
-      </c>
-      <c r="I37" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="38" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D38" t="s">
-        <v>32</v>
-      </c>
-      <c r="H38" s="47">
-        <v>472000</v>
-      </c>
-      <c r="I38" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="39" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D39" t="s">
-        <v>35</v>
-      </c>
-      <c r="H39" s="47">
-        <v>5200000</v>
-      </c>
-      <c r="I39" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="40" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D40" t="s">
-        <v>36</v>
-      </c>
-      <c r="H40" s="47">
-        <v>10400000</v>
-      </c>
-      <c r="I40" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="41" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="K41" s="6"/>
-    </row>
-    <row r="42" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="K42" s="6"/>
-    </row>
-    <row r="43" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="K43" s="6"/>
-    </row>
-    <row r="44" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D44" t="s">
-        <v>39</v>
-      </c>
-      <c r="G44" s="47">
-        <f>H37*H34%</f>
-        <v>104000</v>
-      </c>
-      <c r="H44" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="45" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D45" t="s">
-        <v>40</v>
-      </c>
-      <c r="G45" s="47">
-        <f>H39*H34</f>
-        <v>10400000</v>
-      </c>
-      <c r="H45" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="49" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B49" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="50" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="J50" s="54" t="s">
-        <v>50</v>
-      </c>
-      <c r="K50" s="55">
-        <f>K51/12</f>
-        <v>433333.33333333331</v>
-      </c>
-      <c r="L50" s="8"/>
-      <c r="M50" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="N50" s="8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="51" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="J51" s="54" t="s">
-        <v>53</v>
-      </c>
-      <c r="K51" s="55">
-        <f>H37</f>
-        <v>5200000</v>
-      </c>
-      <c r="L51" s="8"/>
-      <c r="M51" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="N51" s="8" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="52" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="J52" s="54" t="s">
-        <v>51</v>
-      </c>
-      <c r="K52" s="57">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="L52" s="4"/>
-      <c r="M52" s="2">
-        <f>$G$30/12</f>
-        <v>1038.2</v>
-      </c>
-      <c r="N52" s="2">
-        <f>G29</f>
-        <v>35202.17</v>
-      </c>
-    </row>
-    <row r="53" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="J53" s="54" t="s">
-        <v>52</v>
-      </c>
-      <c r="K53" s="57">
-        <v>0.03</v>
-      </c>
-      <c r="L53" s="4"/>
-      <c r="M53" s="1">
-        <v>0</v>
-      </c>
-      <c r="N53" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="J54" s="54" t="s">
-        <v>44</v>
-      </c>
-      <c r="K54" s="58">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="55" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="J55" s="54" t="s">
-        <v>43</v>
-      </c>
-      <c r="K55" s="58">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="57" spans="2:15" ht="39" x14ac:dyDescent="0.25">
-      <c r="G57" s="49" t="s">
-        <v>46</v>
-      </c>
-      <c r="H57" s="49" t="s">
-        <v>45</v>
-      </c>
-      <c r="I57" s="49" t="s">
-        <v>42</v>
-      </c>
-      <c r="J57" s="52" t="s">
-        <v>57</v>
-      </c>
-      <c r="K57" s="52" t="s">
-        <v>58</v>
-      </c>
-      <c r="L57" s="83" t="s">
-        <v>59</v>
-      </c>
-      <c r="M57" s="82" t="s">
-        <v>60</v>
-      </c>
-      <c r="N57" s="52" t="s">
-        <v>54</v>
-      </c>
-      <c r="O57" s="80" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="58" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="G58" s="50">
-        <v>0</v>
-      </c>
-      <c r="H58" s="50">
-        <v>0</v>
-      </c>
-      <c r="I58" s="19">
-        <v>0</v>
-      </c>
-      <c r="J58" s="51">
-        <v>0</v>
-      </c>
-      <c r="K58" s="51">
-        <f>$K$52*(I58/24)^1.5</f>
-        <v>0</v>
-      </c>
-      <c r="L58" s="84">
-        <v>0</v>
-      </c>
-      <c r="M58" s="79">
-        <v>0</v>
-      </c>
-      <c r="N58" s="53">
-        <f>$N$52</f>
-        <v>35202.17</v>
-      </c>
-      <c r="O58" s="81">
-        <f>(M58-L58)-N58</f>
-        <v>-35202.17</v>
-      </c>
-    </row>
-    <row r="59" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="G59" s="50">
-        <f>ROW(H59)-ROW($H$57)-1</f>
-        <v>1</v>
-      </c>
-      <c r="H59" s="50">
-        <f>(100/$K$54)*G59</f>
-        <v>16.666666666666668</v>
-      </c>
-      <c r="I59" s="19">
-        <f>($K$55/$K$54)*G59</f>
-        <v>4</v>
-      </c>
-      <c r="J59" s="51">
-        <f>$K$53*(I59/24)^1.5</f>
-        <v>2.0412414523193144E-3</v>
-      </c>
-      <c r="K59" s="51">
-        <f>$K$52*(I59/24)^1.5</f>
-        <v>9.5257934441568028E-3</v>
-      </c>
-      <c r="L59" s="84">
-        <f>((I59-I58)*(J59*$K$50))+L58</f>
-        <v>3538.1518506868115</v>
-      </c>
-      <c r="M59" s="79">
-        <f>((I59-I58)*(K59*$K$50))+M58</f>
-        <v>16511.375303205125</v>
-      </c>
-      <c r="N59" s="53">
-        <f>($M$52*(I59-I58))+N58</f>
-        <v>39354.97</v>
-      </c>
-      <c r="O59" s="81">
-        <f>(M59-L59)-N59</f>
-        <v>-26381.746547481689</v>
-      </c>
-    </row>
-    <row r="60" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="G60" s="50">
-        <f>ROW(H60)-ROW($H$57)-1</f>
-        <v>2</v>
-      </c>
-      <c r="H60" s="50">
-        <f>(100/$K$54)*G60</f>
-        <v>33.333333333333336</v>
-      </c>
-      <c r="I60" s="19">
-        <f>($K$55/$K$54)*G60</f>
-        <v>8</v>
-      </c>
-      <c r="J60" s="51">
-        <f t="shared" ref="J60:J64" si="5">$K$53*(I60/24)^1.5</f>
-        <v>5.773502691896258E-3</v>
-      </c>
-      <c r="K60" s="51">
-        <f>$K$52*(I60/24)^1.5</f>
-        <v>2.6943012562182539E-2</v>
-      </c>
-      <c r="L60" s="84">
-        <f t="shared" ref="L60:L64" si="6">((I60-I59)*(J60*$K$50))+L59</f>
-        <v>13545.556516640325</v>
-      </c>
-      <c r="M60" s="79">
-        <f>((I60-I59)*(K60*$K$50))+M59</f>
-        <v>63212.597077654857</v>
-      </c>
-      <c r="N60" s="53">
-        <f>($M$52*(I60-I59))+N59</f>
-        <v>43507.770000000004</v>
-      </c>
-      <c r="O60" s="81">
-        <f>(M60-L60)-N60</f>
-        <v>6159.2705610145276</v>
-      </c>
-    </row>
-    <row r="61" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="G61" s="50">
-        <f>ROW(H61)-ROW($H$57)-1</f>
-        <v>3</v>
-      </c>
-      <c r="H61" s="50">
-        <f>(100/$K$54)*G61</f>
-        <v>50</v>
-      </c>
-      <c r="I61" s="19">
-        <f>($K$55/$K$54)*G61</f>
-        <v>12</v>
-      </c>
-      <c r="J61" s="51">
-        <f t="shared" si="5"/>
-        <v>1.0606601717798213E-2</v>
-      </c>
-      <c r="K61" s="51">
-        <f>$K$52*(I61/24)^1.5</f>
-        <v>4.9497474683058332E-2</v>
-      </c>
-      <c r="L61" s="84">
-        <f t="shared" si="6"/>
-        <v>31930.332827490562</v>
-      </c>
-      <c r="M61" s="79">
-        <f>((I61-I60)*(K61*$K$50))+M60</f>
-        <v>149008.21986162264</v>
-      </c>
-      <c r="N61" s="53">
-        <f>($M$52*(I61-I60))+N60</f>
-        <v>47660.570000000007</v>
-      </c>
-      <c r="O61" s="81">
-        <f>(M61-L61)-N61</f>
-        <v>69417.317034132066</v>
-      </c>
-    </row>
-    <row r="62" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="G62" s="50">
-        <f>ROW(H62)-ROW($H$57)-1</f>
-        <v>4</v>
-      </c>
-      <c r="H62" s="50">
-        <f>(100/$K$54)*G62</f>
-        <v>66.666666666666671</v>
-      </c>
-      <c r="I62" s="19">
-        <f>($K$55/$K$54)*G62</f>
-        <v>16</v>
-      </c>
-      <c r="J62" s="51">
-        <f t="shared" si="5"/>
-        <v>1.6329931618554516E-2</v>
-      </c>
-      <c r="K62" s="51">
-        <f>$K$52*(I62/24)^1.5</f>
-        <v>7.6206347553254422E-2</v>
-      </c>
-      <c r="L62" s="84">
-        <f t="shared" si="6"/>
-        <v>60235.54763298505</v>
-      </c>
-      <c r="M62" s="79">
-        <f>((I62-I61)*(K62*$K$50))+M61</f>
-        <v>281099.2222872636</v>
-      </c>
-      <c r="N62" s="53">
-        <f>($M$52*(I62-I61))+N61</f>
-        <v>51813.37000000001</v>
-      </c>
-      <c r="O62" s="81">
-        <f>(M62-L62)-N62</f>
-        <v>169050.30465427856</v>
-      </c>
-    </row>
-    <row r="63" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="G63" s="50">
-        <f>ROW(H63)-ROW($H$57)-1</f>
-        <v>5</v>
-      </c>
-      <c r="H63" s="50">
-        <f>(100/$K$54)*G63</f>
-        <v>83.333333333333343</v>
-      </c>
-      <c r="I63" s="19">
-        <f>($K$55/$K$54)*G63</f>
-        <v>20</v>
-      </c>
-      <c r="J63" s="51">
-        <f t="shared" si="5"/>
-        <v>2.282177322938192E-2</v>
-      </c>
-      <c r="K63" s="51">
-        <f>$K$52*(I63/24)^1.5</f>
-        <v>0.10650160840378231</v>
-      </c>
-      <c r="L63" s="84">
-        <f t="shared" si="6"/>
-        <v>99793.287897247035</v>
-      </c>
-      <c r="M63" s="79">
-        <f>((I63-I62)*(K63*$K$50))+M62</f>
-        <v>465702.01018715295</v>
-      </c>
-      <c r="N63" s="53">
-        <f>($M$52*(I63-I62))+N62</f>
-        <v>55966.170000000013</v>
-      </c>
-      <c r="O63" s="81">
-        <f>(M63-L63)-N63</f>
-        <v>309942.55228990584</v>
-      </c>
-    </row>
-    <row r="64" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="G64" s="50">
-        <f>ROW(H64)-ROW($H$57)-1</f>
-        <v>6</v>
-      </c>
-      <c r="H64" s="50">
-        <f>(100/$K$54)*G64</f>
-        <v>100</v>
-      </c>
-      <c r="I64" s="19">
-        <f>($K$55/$K$54)*G64</f>
-        <v>24</v>
-      </c>
-      <c r="J64" s="51">
-        <f t="shared" si="5"/>
-        <v>0.03</v>
-      </c>
-      <c r="K64" s="51">
-        <f>$K$52*(I64/24)^1.5</f>
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="L64" s="84">
-        <f t="shared" si="6"/>
-        <v>151793.28789724704</v>
-      </c>
-      <c r="M64" s="79">
-        <f>((I64-I63)*(K64*$K$50))+M63</f>
-        <v>708368.67685381963</v>
-      </c>
-      <c r="N64" s="53">
-        <f>($M$52*(I64-I63))+N63</f>
-        <v>60118.970000000016</v>
-      </c>
-      <c r="O64" s="81">
-        <f>(M64-L64)-N64</f>
-        <v>496456.4189565726</v>
-      </c>
-    </row>
-    <row r="71" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="H71" s="56"/>
-    </row>
-    <row r="72" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B72" s="61" t="s">
-        <v>61</v>
-      </c>
-      <c r="C72" s="3"/>
-      <c r="D72" s="62" t="s">
-        <v>24</v>
-      </c>
-      <c r="H72" s="65" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="73" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B73" s="61" t="s">
-        <v>62</v>
-      </c>
-      <c r="C73" s="3"/>
-      <c r="D73" s="62" t="s">
-        <v>28</v>
-      </c>
-      <c r="E73" s="60"/>
-      <c r="H73" s="65" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="74" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B74" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C74" s="3"/>
-      <c r="D74" s="63" t="s">
-        <v>28</v>
-      </c>
-      <c r="H74" s="65" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="75" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B75" s="61" t="s">
-        <v>64</v>
-      </c>
-      <c r="C75" s="3"/>
-      <c r="D75" s="62" t="s">
-        <v>28</v>
-      </c>
-      <c r="E75" s="60"/>
-      <c r="H75" s="65" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="76" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B76" s="64" t="s">
-        <v>65</v>
-      </c>
-      <c r="C76" s="3"/>
-      <c r="D76" s="62" t="s">
-        <v>26</v>
-      </c>
-      <c r="H76" s="65" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="77" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B77" s="61" t="s">
-        <v>66</v>
-      </c>
-      <c r="C77" s="3"/>
-      <c r="D77" s="62" t="s">
-        <v>28</v>
-      </c>
-      <c r="H77" s="65" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="78" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B78" s="61" t="s">
-        <v>67</v>
-      </c>
-      <c r="C78" s="3"/>
-      <c r="D78" s="63" t="s">
-        <v>68</v>
-      </c>
-      <c r="H78" s="65" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="79" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B79" s="59"/>
-      <c r="C79" s="5"/>
-      <c r="D79" s="5"/>
-      <c r="H79" s="56"/>
-    </row>
-    <row r="80" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B80" s="5"/>
-      <c r="C80" s="5"/>
-      <c r="D80" s="5"/>
-      <c r="H80" s="56"/>
-    </row>
-    <row r="81" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B81" s="5"/>
-      <c r="C81" s="5"/>
-      <c r="D81" s="5"/>
-      <c r="H81" s="56"/>
-    </row>
-    <row r="82" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B82" s="5"/>
-      <c r="C82" s="5"/>
-      <c r="D82" s="5"/>
-      <c r="H82" s="56"/>
+      <c r="I95" s="64"/>
+    </row>
+    <row r="96" spans="2:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B96" s="33"/>
+      <c r="C96" s="2"/>
+      <c r="D96" s="2"/>
+    </row>
+    <row r="97" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B97" s="2"/>
+      <c r="C97" s="2"/>
+      <c r="D97" s="2"/>
+    </row>
+    <row r="98" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B98" s="2"/>
+      <c r="C98" s="2"/>
+      <c r="D98" s="2"/>
+    </row>
+    <row r="99" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B99" s="2"/>
+      <c r="C99" s="2"/>
+      <c r="D99" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="H32:I32"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="K12:L12"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="K13:L13"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="K23:L23"/>
+    <mergeCell ref="K24:L24"/>
+    <mergeCell ref="H57:I57"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="K36:L36"/>
+    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="K37:L37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+  <ignoredErrors>
+    <ignoredError sqref="K28:K30 G28:G29 G31:G33 I28:I29 K32:K33" formulaRange="1"/>
+    <ignoredError sqref="N10 H66" formula="1"/>
+  </ignoredErrors>
   <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53C03833-3A5E-461C-AFD0-2ACB4E7497F1}">
+  <dimension ref="O3:Y19"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="5.7109375" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="16" max="16" width="1.5703125" customWidth="1"/>
+    <col min="24" max="24" width="1.28515625" customWidth="1"/>
+    <col min="25" max="25" width="16" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="15:25" ht="138" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q3" s="72" t="s">
+        <v>4</v>
+      </c>
+      <c r="R3" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="S3" s="72" t="s">
+        <v>3</v>
+      </c>
+      <c r="T3" s="72" t="s">
+        <v>2</v>
+      </c>
+      <c r="U3" s="73" t="s">
+        <v>81</v>
+      </c>
+      <c r="V3" s="73" t="s">
+        <v>82</v>
+      </c>
+      <c r="W3" s="73" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="4" spans="15:25" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="5" spans="15:25" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="O5" s="61" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q5" s="69" t="s">
+        <v>69</v>
+      </c>
+      <c r="R5" s="69" t="s">
+        <v>69</v>
+      </c>
+      <c r="S5" s="70" t="s">
+        <v>70</v>
+      </c>
+      <c r="T5" s="68" t="s">
+        <v>71</v>
+      </c>
+      <c r="U5" s="66"/>
+      <c r="V5" s="66"/>
+      <c r="W5" s="66"/>
+      <c r="Y5" s="135" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="15:25" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="O6" s="61" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q6" s="69" t="s">
+        <v>69</v>
+      </c>
+      <c r="R6" s="65"/>
+      <c r="S6" s="70" t="s">
+        <v>70</v>
+      </c>
+      <c r="T6" s="66"/>
+      <c r="U6" s="66"/>
+      <c r="V6" s="66"/>
+      <c r="W6" s="68" t="s">
+        <v>71</v>
+      </c>
+      <c r="Y6" s="135"/>
+    </row>
+    <row r="7" spans="15:25" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="O7" s="61" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q7" s="67"/>
+      <c r="R7" s="67"/>
+      <c r="S7" s="68" t="s">
+        <v>71</v>
+      </c>
+      <c r="T7" s="69" t="s">
+        <v>69</v>
+      </c>
+      <c r="U7" s="69" t="s">
+        <v>69</v>
+      </c>
+      <c r="V7" s="69" t="s">
+        <v>69</v>
+      </c>
+      <c r="W7" s="70" t="s">
+        <v>70</v>
+      </c>
+      <c r="Y7" s="136" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="15:25" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="O8" s="61" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q8" s="67"/>
+      <c r="R8" s="69" t="s">
+        <v>69</v>
+      </c>
+      <c r="S8" s="68" t="s">
+        <v>71</v>
+      </c>
+      <c r="T8" s="69" t="s">
+        <v>69</v>
+      </c>
+      <c r="U8" s="66"/>
+      <c r="V8" s="66"/>
+      <c r="W8" s="66"/>
+      <c r="Y8" s="136"/>
+    </row>
+    <row r="9" spans="15:25" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="O9" s="61" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q9" s="68" t="s">
+        <v>71</v>
+      </c>
+      <c r="R9" s="68" t="s">
+        <v>71</v>
+      </c>
+      <c r="S9" s="71" t="s">
+        <v>72</v>
+      </c>
+      <c r="T9" s="69" t="s">
+        <v>69</v>
+      </c>
+      <c r="U9" s="66"/>
+      <c r="V9" s="69" t="s">
+        <v>69</v>
+      </c>
+      <c r="W9" s="70" t="s">
+        <v>70</v>
+      </c>
+      <c r="Y9" s="136"/>
+    </row>
+    <row r="10" spans="15:25" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="O10" s="61" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q10" s="67"/>
+      <c r="R10" s="67"/>
+      <c r="S10" s="71" t="s">
+        <v>72</v>
+      </c>
+      <c r="T10" s="69" t="s">
+        <v>69</v>
+      </c>
+      <c r="U10" s="66"/>
+      <c r="V10" s="66"/>
+      <c r="W10" s="66"/>
+      <c r="Y10" s="137" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="15:25" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="O11" s="61" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q11" s="67"/>
+      <c r="R11" s="67"/>
+      <c r="S11" s="71" t="s">
+        <v>72</v>
+      </c>
+      <c r="T11" s="69" t="s">
+        <v>69</v>
+      </c>
+      <c r="U11" s="66"/>
+      <c r="V11" s="66"/>
+      <c r="W11" s="66"/>
+      <c r="Y11" s="137"/>
+    </row>
+    <row r="12" spans="15:25" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="O12" s="61" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q12" s="68" t="s">
+        <v>71</v>
+      </c>
+      <c r="R12" s="68" t="s">
+        <v>71</v>
+      </c>
+      <c r="S12" s="70" t="s">
+        <v>70</v>
+      </c>
+      <c r="T12" s="69" t="s">
+        <v>69</v>
+      </c>
+      <c r="U12" s="66"/>
+      <c r="V12" s="66"/>
+      <c r="W12" s="66"/>
+      <c r="Y12" s="137"/>
+    </row>
+    <row r="13" spans="15:25" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="O13" s="61" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q13" s="69" t="s">
+        <v>69</v>
+      </c>
+      <c r="R13" s="68" t="s">
+        <v>71</v>
+      </c>
+      <c r="S13" s="68" t="s">
+        <v>71</v>
+      </c>
+      <c r="T13" s="67"/>
+      <c r="U13" s="66"/>
+      <c r="V13" s="66"/>
+      <c r="W13" s="66"/>
+      <c r="Y13" s="137"/>
+    </row>
+    <row r="16" spans="15:25" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q16" t="s">
+        <v>69</v>
+      </c>
+      <c r="R16" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="17" spans="17:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q17" t="s">
+        <v>70</v>
+      </c>
+      <c r="R17" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="18" spans="17:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q18" t="s">
+        <v>71</v>
+      </c>
+      <c r="R18" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="19" spans="17:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q19" t="s">
+        <v>72</v>
+      </c>
+      <c r="R19" t="s">
+        <v>76</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="Y5:Y6"/>
+    <mergeCell ref="Y7:Y9"/>
+    <mergeCell ref="Y10:Y13"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>